--- a/reports/pdf_change_20260908.xlsx
+++ b/reports/pdf_change_20260908.xlsx
@@ -574,7 +574,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,584억   ·   현금 21억(0.4%)      당일 2026-09-08  vs  전영업일 2026-09-07      매수 3종목  /  매도 1종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,584억      당일 2026-09-08  vs  전영업일 2026-09-07      매수 3종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -763,7 +763,7 @@
     <row r="10" ht="19" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,588억   ·   현금 44억(1.2%)      당일 2026-09-08  vs  전영업일 2026-09-07      매수 0종목  /  매도 0종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,588억      당일 2026-09-08  vs  전영업일 2026-09-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B10" s="4" t="n"/>
@@ -787,7 +787,7 @@
     <row r="13" ht="19" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,559억   ·   현금 34억(1.3%)      당일 2026-09-08  vs  전영업일 2026-09-07      매수 9종목  /  매도 6종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,559억      당일 2026-09-08  vs  전영업일 2026-09-07      매수 9종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B13" s="4" t="n"/>
@@ -1096,23 +1096,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈  (신규)</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2710447500</v>
+        <v>3125047500</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.31%→3.58%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1140,23 +1140,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>로보티즈  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>3125047500</v>
+        <v>2710447500</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>2.31%→3.58%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>0→15</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G22" s="17" t="n"/>
@@ -1224,7 +1224,7 @@
     <row r="26" ht="19" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,028억   ·   현금 16억(0.8%)      당일 2026-09-08  vs  전영업일 2026-09-07      매수 4종목  /  매도 6종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,028억      당일 2026-09-08  vs  전영업일 2026-09-07      매수 4종목  /  매도 6종목</t>
         </is>
       </c>
       <c r="B26" s="4" t="n"/>
@@ -1545,7 +1545,7 @@
     <row r="36" ht="19" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억   ·   현금 1억(0.5%)      당일 2026-09-08  vs  전영업일 2026-09-07      매수 1종목  /  매도 1종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 274억      당일 2026-09-08  vs  전영업일 2026-09-07      매수 1종목  /  매도 1종목</t>
         </is>
       </c>
       <c r="B36" s="4" t="n"/>
@@ -1678,7 +1678,7 @@
     <row r="41" ht="19" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 502억   ·   현금 4억(0.8%)      당일 2026-09-08  vs  전영업일 2026-09-07      매수 0종목  /  매도 0종목</t>
+          <t>■ RISE 바이오TOP10액티브  (KB)      순자산 ≈ 502억      당일 2026-09-08  vs  전영업일 2026-09-07      매수 0종목  /  매도 0종목</t>
         </is>
       </c>
       <c r="B41" s="4" t="n"/>

--- a/reports/pdf_change_20260908.xlsx
+++ b/reports/pdf_change_20260908.xlsx
@@ -1096,23 +1096,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>로보티즈  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>3125047500</v>
+        <v>2710447500</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>2.31%→3.58%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>0→15</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1140,23 +1140,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈  (신규)</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>2710447500</v>
+        <v>3125047500</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>2.31%→3.58%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G22" s="17" t="n"/>

--- a/reports/pdf_change_20260908.xlsx
+++ b/reports/pdf_change_20260908.xlsx
@@ -1096,23 +1096,23 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>로보티즈  (신규)</t>
         </is>
       </c>
       <c r="B21" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2710447500</v>
+        <v>3125047500</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>2.31%→3.58%</t>
+          <t>0.00%→1.24%</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>35→50</t>
+          <t>0→15</t>
         </is>
       </c>
       <c r="G21" s="14" t="inlineStr">
@@ -1140,23 +1140,23 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>로보티즈  (신규)</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="B22" s="11" t="n">
         <v>15</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>3125047500</v>
+        <v>2710447500</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.24%</t>
+          <t>2.31%→3.58%</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>0→15</t>
+          <t>35→50</t>
         </is>
       </c>
       <c r="G22" s="17" t="n"/>
